--- a/e_commerce_forms/015_ecommerce_domain_name_suggestion_request--e_commerce_forms.xlsx
+++ b/e_commerce_forms/015_ecommerce_domain_name_suggestion_request--e_commerce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'amazon'}</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Amazon'}</t>
+          <t>Amazon</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'flipkart'}</t>
+          <t>flipkart</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Flipkart'}</t>
+          <t>Flipkart</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'flip'}</t>
+          <t>flip</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Flip'}</t>
+          <t>Flip</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'flipa'}</t>
+          <t>flipa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Flipa'}</t>
+          <t>Flipa</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'flipb'}</t>
+          <t>flipb</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Flipb'}</t>
+          <t>Flipb</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'food'}</t>
+          <t>food</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Food'}</t>
+          <t>Food</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'electronics'}</t>
+          <t>electronics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Electronics'}</t>
+          <t>Electronics</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'fashion'}</t>
+          <t>fashion</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Fashion'}</t>
+          <t>Fashion</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'health'}</t>
+          <t>health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Health'}</t>
+          <t>Health</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'beauty'}</t>
+          <t>beauty</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Beauty'}</t>
+          <t>Beauty</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'fruits'}</t>
+          <t>fruits</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Fruits'}</t>
+          <t>Fruits</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'vegetables'}</t>
+          <t>vegetables</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Vegetables'}</t>
+          <t>Vegetables</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'electronics'}</t>
+          <t>electronics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Electronics'}</t>
+          <t>Electronics</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'accessories'}</t>
+          <t>accessories</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Accessories'}</t>
+          <t>Accessories</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'usa'}</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'USA'}</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'usa1'}</t>
+          <t>usa1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'USA1'}</t>
+          <t>USA1</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'usa2'}</t>
+          <t>usa2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'USA2'}</t>
+          <t>USA2</t>
         </is>
       </c>
     </row>
